--- a/AAII_Financials/Quarterly/BNS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>BNS</t>
   </si>
@@ -656,274 +656,280 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6740500</v>
+      </c>
+      <c r="E8" s="3">
         <v>6332600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6236300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5212000</v>
       </c>
-      <c r="G8" s="3">
-        <v>6102100</v>
-      </c>
       <c r="H8" s="3">
+        <v>6118700</v>
+      </c>
+      <c r="I8" s="3">
         <v>5540500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4731500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5281700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5293400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5340500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5584200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5315800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5510100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5312300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9684300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8102400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6565900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5156000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4698700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4582200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4519300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4645600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4889600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5099700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5355700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6153200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6421400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6433800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6997200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6236300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6151600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5610000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5368100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5070000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4823200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4649100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4553100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4481900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4400400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4378100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1044,53 +1050,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6740500</v>
+      </c>
+      <c r="E10" s="3">
         <v>6332600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6236300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5212000</v>
       </c>
-      <c r="G10" s="3">
-        <v>6102100</v>
-      </c>
       <c r="H10" s="3">
+        <v>6118700</v>
+      </c>
+      <c r="I10" s="3">
         <v>5540500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4731500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5281700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5293400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5340500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5584200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5315800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5510100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5312300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1166,8 +1175,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1210,8 +1222,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1332,8 +1345,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1454,8 +1470,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1498,8 +1517,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1576,130 +1595,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>283700</v>
+      </c>
+      <c r="E15" s="3">
         <v>301200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>283800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>81700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>292600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>284400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>278400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>84500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>309800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>298300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>314700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>104200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>313200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>303800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-314300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-304600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-299300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-294400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-290800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-302200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-294100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-301100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-306400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-332000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-309000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-306200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-332100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-233100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-253700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-220200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-214000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-188900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-176900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-167100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-148100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-145100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-142100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-144400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-143700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-140600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1739,252 +1764,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3960500</v>
+      </c>
+      <c r="E17" s="3">
         <v>3812000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3898500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3169700</v>
       </c>
-      <c r="G17" s="3">
-        <v>3677200</v>
-      </c>
       <c r="H17" s="3">
+        <v>3693800</v>
+      </c>
+      <c r="I17" s="3">
         <v>3679200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3543800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3702900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3582800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3427700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3542100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4243700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3465800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3372900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6795000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5119500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3414900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2063300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1701900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1583000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1677000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1882400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2196300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2412600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2641800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3371000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3719000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3640300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3962000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3680500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3391100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2972200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3002900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2498500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2298900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2196900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2127000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2068800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2026600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1994300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2780000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2520500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2337800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2042300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2424900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1861300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1187700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1578800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1710700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1912800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2042000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1072100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2044200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1939400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2889200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2982800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3151100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3092700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2996700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2999300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2842200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2763200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2693300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2687100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2713900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2782200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2702300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2793600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3035200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2555800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2760600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2637900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2365300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2571500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2524400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2452200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2426100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2413000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2373800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2027,8 +2059,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2071,208 +2104,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-781700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1111400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-789200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-501600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-376600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-593300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-412600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-361900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-365700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-910800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1537100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1410700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-521600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-529400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-766000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-335600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-647400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-607500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-507400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-465200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-257500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-511300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-454700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-574600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-356500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-424100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3063700</v>
+      </c>
+      <c r="E21" s="3">
         <v>2821700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2621600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2124000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2717600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2145700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1466200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1663300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2020500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2211100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2356700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1176300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2357400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2243200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2406300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2158600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2643400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2868100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2892800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2689600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2705900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2682800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2613000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2088300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1465800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1656500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2491800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2475500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2497900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2418800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2304100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2199700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2017500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2259900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2415000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2086000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2113600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1982800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2161000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2100300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2315,8 +2354,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2393,252 +2432,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2780000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2520500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2337800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2042300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2424900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1861300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1187700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1578800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1710700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1912800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2042000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1072100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2044200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1939400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2107500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1871500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2361800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2591100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2620100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2405900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2429600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2401300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2327700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1776300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1176800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1371500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2180700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2264200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2269100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2220200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2113200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2030400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1857900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2106300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2266900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1940900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1971400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1838400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2017400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1959800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>675000</v>
+      </c>
+      <c r="E24" s="3">
         <v>587000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>642900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>468100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>599000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>390800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>501600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>366700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>326500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>390700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>398400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>97200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>377800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>356900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>813400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>346200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>444900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>594000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>628100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>510400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>546700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>557100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>527100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>320500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>177100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>332100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>367200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>464700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>624300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>481100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>383400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>380100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>398200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>467500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>527600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>400400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>406300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>255100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>474000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2759,252 +2807,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2105000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1933600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1694900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1574200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1825900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1470500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>686100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1212100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1384200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1522100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1643600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>974900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1666400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1582500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1294100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1525300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1916900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1997100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1992000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1895600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1883000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1844100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1800600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1455800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>999700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1039400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1813500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1799500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1644800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1739000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1729800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1650300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1459700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1638800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1739200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1540500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1565100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1583300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1543400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1544900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1980200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1813100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1588800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1501400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1655400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1332300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>708200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1091500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1271200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1413700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1544200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>874100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1571400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1488100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1192500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1420400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1850400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1886600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1896000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1785900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1797000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1718700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1700700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1337800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1021200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>975800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1763600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1666200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1524600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1635900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1622000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1536200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1472500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1537200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1673700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1500300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1509600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1466600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1465800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3125,8 +3182,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3247,8 +3307,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3369,8 +3432,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3491,8 +3557,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3535,208 +3604,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>781700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1111400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>789200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>501600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>376600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>593300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>412600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>361900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>365700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>910800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1537100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1410700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>521600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>529400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>766000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>335600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>647400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>607500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>507400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>465200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>257500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>511300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>454700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>574600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>356500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2072900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1906400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1686100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1583400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1768100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1430000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>792500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1178300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1358100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1503200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1624900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>952600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1651200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1564800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1192500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1420400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1850400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1886600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1896000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1785900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1797000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1718700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1700700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1337800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1021200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>975800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1763600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1666200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1524600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1635900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1622000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1536200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1472500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1537200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1673700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1500300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1509600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1466600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1465800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3857,257 +3932,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2072900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1906400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1686100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1583400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1768100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1430000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>792500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1178300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1358100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1503200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1624900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>952600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1651200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1564800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1192500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1420400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1850400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1886600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1896000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1785900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1797000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1718700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1700700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1337800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1021200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>975800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1763600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1666200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1524600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1635900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1622000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1536200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1472500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1537200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1673700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1500300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1509600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1466600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1465800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4150,8 +4234,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4194,252 +4279,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3068700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2485300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2592100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2495400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3082500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7821600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2835600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2930700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2711900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2875400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2610100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3178800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5012900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2397300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6110400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8063700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6956100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7737600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7679400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7180000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6335500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5961800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7090400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8527300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8502800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9156000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7978400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8501500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8744800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7436500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7543500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6538000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6020800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5560100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5828700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5823400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5103800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6764300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6125100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>5266200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>384084800</v>
+      </c>
+      <c r="E42" s="3">
         <v>387720600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>360743400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>326444600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>306099900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>300951600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>304220900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>307931800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>301780200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>304755500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>316242000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>323045900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>334499500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>294006400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>305754300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>292398200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>282162600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>301657500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>302919600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>292585600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>282436000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>271490000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>292090500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>268623800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>274213300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>326294300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>310629100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>262831400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>269948600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>245269300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>241611900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>216781100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>195829300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>207922900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>208904200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>209121500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>207952400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>225427900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>214720300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>216684600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4449,41 +4541,41 @@
       <c r="E43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3">
         <v>7133000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>5551500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O43" s="3">
         <v>6725600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4560,8 +4652,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4571,41 +4666,41 @@
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
         <v>157700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>223900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
         <v>240500</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4682,53 +4777,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4326100</v>
+      </c>
+      <c r="E45" s="3">
         <v>7607100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8637500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16844800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4310100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4457900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2690500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12928600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4127200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7545100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12560800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26442900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16294500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17028100</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4804,53 +4902,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>395773700</v>
+      </c>
+      <c r="E46" s="3">
         <v>402015100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>375818500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>357898600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>318878600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>317909000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>313749600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>333385700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>312606000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>319408500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>335687500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>363779400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>360399400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>317886500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4926,374 +5027,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>114678500</v>
+      </c>
+      <c r="E47" s="3">
         <v>115680100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>110569800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>111507900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112128300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>115904400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>109830700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>110981700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>111402100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>106847400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>106298700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>86517200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>85754300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>87974400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1975700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1918800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2019700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2006500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1992000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1928900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1854800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1862100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1889200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1897400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1839200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1909200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1814300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4377100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4556500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4082400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3990700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3524400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3540400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3617900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3362300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3412900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>3261100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>3474700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>3274200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3302600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3966200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3903900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3888900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3483000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3463300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3480200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3387000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3768900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3897700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3996700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4125200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4062300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4321800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4163400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4195100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4153900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4085900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4050200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4058200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4163700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4102200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4173300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4302400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4520900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4619000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4807600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4758300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2080900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2183700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2095500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2063100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1950400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1955000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1799200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1722100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1772000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1658100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1809200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1747700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1935900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11413700</v>
+      </c>
+      <c r="E49" s="3">
         <v>11732100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11885800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11537900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11609500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11643300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11205600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12094000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12284500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12408300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12692400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12379000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13122900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12827900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12639000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12267200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12252500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12149800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12178900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12299200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12372600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12615200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12747400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>13044400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>13137100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>13433800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>13403300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>13616900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>14601200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>13722000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>13752100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>12876200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11209000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9239000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8967000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9009400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>8879200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>9437700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9261800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>9327100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5414,8 +5527,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5536,130 +5652,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26330300</v>
+      </c>
+      <c r="E52" s="3">
         <v>25690200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26600400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4907300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23649000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25902800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24723100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4969500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23115400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24778800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23902600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6010600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23499900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24705200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1846200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1386800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>668800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>826600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1431500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1519300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1561500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1540800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1588800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1675100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1659000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1311000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1339500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1224100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1414400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1592800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1575800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1408300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1473200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1345200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1293400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1274800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1286000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1485000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1379000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1552600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5780,130 +5902,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1103642500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1117762700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1088151100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1041860200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1022208900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1024348300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>994362600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1013295300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1015228800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1018211600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1041106500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1015957500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1061340600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1012600700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1011737600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>983401900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>954850500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>936756700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>905472100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>877661300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>861798400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>844903700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>874038600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>871260300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>896870700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>979014700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>899756300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>846847100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>884380800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>814599700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>796211700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>725594900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>712668600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>697316900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>687018900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>681155300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>674501300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>708036100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>681413900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>688538400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5946,8 +6074,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5990,53 +6119,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>717112100</v>
+      </c>
+      <c r="E57" s="3">
         <v>721036300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>716363000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>696049600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>684159100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>684490700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>667479000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>683159000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>687164500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>685410400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>702429200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>691691100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>727700900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>697242800</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6112,59 +6242,62 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>41589000</v>
+      </c>
+      <c r="E58" s="3">
         <v>41766900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>201192900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>183329300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>177446400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>180583600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>174054600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>178895600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>170296000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>169357500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>161011000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>161247900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>154447700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>138553700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>102735900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>106531600</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
@@ -6234,53 +6367,56 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>115500</v>
+      </c>
+      <c r="E59" s="3">
         <v>115300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6756100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11346700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8233700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8417200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6882400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11054200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10695500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18963200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25073100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25626400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26432100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26906400</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
@@ -6356,53 +6492,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>758816600</v>
+      </c>
+      <c r="E60" s="3">
         <v>762918600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>924312000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>896933000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>869839200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>873491500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>848416000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>879307500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>868156100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>873731100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>888513300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>885226200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>908580600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>862702900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6478,175 +6617,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>203899100</v>
+      </c>
+      <c r="E61" s="3">
         <v>215290700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32123000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32876900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29410000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27068600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26138800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28399000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26202300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25330300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25332400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24758800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25525900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22872800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32971800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30433700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6217100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6141100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4607800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4691800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4754100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4834800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4955700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5677000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5624100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5875300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5687700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5654200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7478900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5815200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5767500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4140700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4281100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4266100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4242700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4416900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5489300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5854700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5767100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5863900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76329200</v>
+      </c>
+      <c r="E62" s="3">
         <v>74478000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66085500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>47445400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>61192200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61185200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60096300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43876600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>60624900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>60160800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67127300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47984700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>68151400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>68954600</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6722,8 +6867,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6844,8 +6992,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6966,8 +7117,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7088,130 +7242,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1039045000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1052687300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1022520500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>978646000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>960441500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>961745400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>934651200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>952960900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>954983200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>959222200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>980973000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>959386000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1002257900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>954530200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>957127800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>930038400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>901573000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>885586100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>853328000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>825215500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>809932500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>793839200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>822458300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>819031400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>844592700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>925723100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>847230700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>794202300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>828487900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>762671500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>745088800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>678194300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>663747700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>651024100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>642619400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>636478200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>632539800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>663375800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>638197100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>645324700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7254,8 +7414,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7376,8 +7537,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7498,8 +7662,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7534,94 +7701,97 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>216000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>228100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>221200</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>5944100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>5884700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>5211400</v>
-      </c>
-      <c r="T70" s="3">
-        <v>4036400</v>
       </c>
       <c r="U70" s="3">
         <v>4036400</v>
       </c>
       <c r="V70" s="3">
+        <v>4036400</v>
+      </c>
+      <c r="W70" s="3">
         <v>4483000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>3925200</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>3415700</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>3985600</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>4069300</v>
       </c>
       <c r="AA70" s="3">
         <v>4069300</v>
       </c>
       <c r="AB70" s="3">
+        <v>4069300</v>
+      </c>
+      <c r="AC70" s="3">
         <v>2841100</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>3028200</v>
       </c>
       <c r="AD70" s="3">
         <v>3028200</v>
       </c>
       <c r="AE70" s="3">
+        <v>3028200</v>
+      </c>
+      <c r="AF70" s="3">
         <v>3220000</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>2990000</v>
       </c>
       <c r="AG70" s="3">
         <v>2990000</v>
       </c>
       <c r="AH70" s="3">
+        <v>2990000</v>
+      </c>
+      <c r="AI70" s="3">
         <v>3040500</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>3187300</v>
       </c>
       <c r="AJ70" s="3">
         <v>3187300</v>
       </c>
       <c r="AK70" s="3">
-        <v>3407700</v>
+        <v>3187300</v>
       </c>
       <c r="AL70" s="3">
         <v>3407700</v>
       </c>
       <c r="AM70" s="3">
+        <v>3407700</v>
+      </c>
+      <c r="AN70" s="3">
         <v>2246800</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>2319300</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>2496000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>2761000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7742,130 +7912,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>43048200</v>
+      </c>
+      <c r="E72" s="3">
         <v>43987000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>43717600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>42041400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>42417000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>41948300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39690900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41443100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>41656200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41531600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>42188100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40084800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>42407300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40532800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39764700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>39068100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40270500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37854000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37859000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38204400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37194800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36837900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35947400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35805900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35303000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35967100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35693300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34932300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36521300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33449400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32826700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30388700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30724400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30016700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>28815800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>28453400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>27695800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>27932800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>27496500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>26814300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7986,8 +8162,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8108,8 +8287,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8230,130 +8412,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63549000</v>
+      </c>
+      <c r="E76" s="3">
         <v>64031500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64573400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61986000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>60552800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61453700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>58588000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59109400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59004000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57738600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>58865800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55110600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57591900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56670900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48665700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47478700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48066100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>47134200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48107700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47962900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47940700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47648800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47594800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>48159600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>48208600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>50450500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>49497300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>49616600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52672900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>48938200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>48133000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>44360100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>45733500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>43105500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>40991800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>41269400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>39714800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>42341000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>40720800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>40452700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8474,257 +8662,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2072900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1906400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1686100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1583400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1768100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1430000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>792500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1178300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1358100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1503200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1624900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>952600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1651200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1564800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1192500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1420400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1850400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1886600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1896000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1785900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1797000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1718700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1700700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1337800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1021200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>975800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1763600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1666200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1524600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1635900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1622000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1536200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1472500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1537200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1673700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1500300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1509600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1466600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1465800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8767,130 +8964,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>274600</v>
+      </c>
+      <c r="E83" s="3">
         <v>265600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>278400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-328000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>297500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>285200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>301200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-195800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>298000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>288300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>288700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-213400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>278500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>278600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>298900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>287100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>281600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>277000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>272600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>283700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>276300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>281600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>285300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>312000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>289000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>285000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>311100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>211300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>228800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>198600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>190900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>169300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>159600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>153600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>148100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>145100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>142100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>144400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>143700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>140600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9011,8 +9212,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9133,8 +9337,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9255,8 +9462,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9377,8 +9587,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9499,130 +9712,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21738300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1973200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14727800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13641600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2142400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3865900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2291100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10593500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2841500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4350300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-260100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20782900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>973100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>980000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12038300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1725000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7331500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6742300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14508900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4442200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14863700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-34166400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4980500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6788600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-31314200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>56085500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13420500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3169400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5834000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1967700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-8936800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13302100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-8250600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1346000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6458300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-67700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>10880400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-4796100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>6374800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-18996000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9665,116 +9884,117 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-90500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-91800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-170300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-107000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-86800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-86800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-97000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-64000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-109100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-110200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-165000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-177000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-196000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-153000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-45000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-191000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-89000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-102900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-33800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-155600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-126500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-241800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-74100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-115400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>54700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-141700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-79800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-68500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM91" s="3" t="s">
         <v>5</v>
       </c>
@@ -9784,11 +10004,14 @@
       <c r="AO91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AP91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ91" s="3">
         <v>-83000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9909,8 +10132,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10031,130 +10257,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13575700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10323100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7716000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3325300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>121400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>616600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2841100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4462100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3949800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3941400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-891700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4549700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15522900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>11628100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14038400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3675900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5756700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5784800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11755800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4048900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14534800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>34384100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4511200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5552000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>29174500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55092500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-13328500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-790600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5533100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1522700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>8880600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11479500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>8039800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-811500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5603900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>498600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-11229400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>4276700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2833200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>16361800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10197,130 +10429,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1084200</v>
+      </c>
+      <c r="E96" s="3">
         <v>1086500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1001200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>971200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1084600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1053700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>912000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>941500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1030900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>962000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
         <v>981500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-978300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-971400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-934800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-922600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-909500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-868900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-835600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-877800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-851500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-899300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-853300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-907500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-870900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-853000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-880500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-818300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-801400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-757900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-761100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-739200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-728600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-630300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-699600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-727500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-717500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-709800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10441,8 +10677,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10563,8 +10802,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10685,370 +10927,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8905300</v>
+      </c>
+      <c r="E100" s="3">
         <v>8664300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21369600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9141700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1632300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3597400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5281500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5995000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6425700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7973700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>585200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18077900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17203000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11951100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-135400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-969300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>777400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-900000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2226800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>522200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1125500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1591100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1866000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-602700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2052900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1164800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-665900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>619700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6303300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>6132200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1036600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-718200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>174100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-746400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>872700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2534400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>469400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-225800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>190000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-26600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>88000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-152500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>72000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-111800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>73700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>102700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>223700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-117800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>222300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-111600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>106100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-71100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>24400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-220800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-139700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-73600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-164800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>155400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-127700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>113900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>53900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-77800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>13600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>166400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-131000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>114600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-353500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>285800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-148300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>873900</v>
+      </c>
+      <c r="E102" s="3">
         <v>272500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1123600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1044700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>659000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>659300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>339300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>109800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-373600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>406000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-719000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1772700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2541400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>730800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2034600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1203900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-909000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>58200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>632500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>844400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>454100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1128500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1261400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-438500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1122600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-523200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>277600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>736200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-107000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>617400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>726000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>460700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-335700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>5200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>719700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1449000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>639200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>858900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-460900</v>
       </c>
     </row>
